--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:03</t>
+    <t xml:space="preserve">2026-09-09 19:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:31</t>
+    <t xml:space="preserve">2026-09-17 03:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 03:59</t>
+    <t xml:space="preserve">2026-09-27 02:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:24</t>
+    <t xml:space="preserve">2026-10-03 00:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2018_arica_y_parinacota.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 00:20</t>
+    <t xml:space="preserve">2026-10-05 05:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
